--- a/test_samples/YJE_TATA/sample5_ref.xlsx
+++ b/test_samples/YJE_TATA/sample5_ref.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffrey.hu\Desktop\LC\供應商帳單\01. TATA__________OK, 有BL#, 有一張YJE的帳單, 個別以及合併帳單\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffrey.hu\Desktop\印尼供應商帳單\01. TATA__________OK, 有BL#, 有一張YJE的帳單, 個別以及合併帳單\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{254D38C9-B723-425D-AF59-13A1D43B0BC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1EE8D39-53B3-430A-A211-5C552DF8FB23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11505" yWindow="-12945" windowWidth="23505" windowHeight="10995" tabRatio="819" xr2:uid="{B2E6A21A-966E-4572-9141-AA1879003F42}"/>
+    <workbookView xWindow="26160" yWindow="-11325" windowWidth="14730" windowHeight="9270" tabRatio="819" xr2:uid="{B2E6A21A-966E-4572-9141-AA1879003F42}"/>
   </bookViews>
   <sheets>
     <sheet name="DWIHARTA" sheetId="3" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="57">
   <si>
     <t>INVOICE DATE
 發票日期</t>
@@ -123,9 +123,6 @@
     <t>HC2608-2434</t>
   </si>
   <si>
-    <t>HC2608-2436</t>
-  </si>
-  <si>
     <t>PT POU YUEN INDONESIA</t>
   </si>
   <si>
@@ -138,21 +135,12 @@
     <t>CX3249</t>
   </si>
   <si>
-    <t>IDEX15641</t>
-  </si>
-  <si>
-    <t>1 PKG / 3.5 KG</t>
-  </si>
-  <si>
     <t>CX0777</t>
   </si>
   <si>
     <t>Taiwan</t>
   </si>
   <si>
-    <t>2 PKG / 34.5 KG</t>
-  </si>
-  <si>
     <t>BR0237</t>
   </si>
   <si>
@@ -171,32 +159,58 @@
     <t>HANDLING FEE</t>
   </si>
   <si>
-    <t>DPP</t>
-  </si>
-  <si>
     <t>160-13993884</t>
   </si>
   <si>
     <t>N/A</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>3 PKG / 32 KG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HC2608-2435</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HANDLING FEE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>160-13995601</t>
-  </si>
-  <si>
-    <t>695-56377392</t>
+  </si>
+  <si>
+    <t>HC2608-2442</t>
+  </si>
+  <si>
+    <t>YJE123963650</t>
+  </si>
+  <si>
+    <t>160-13993840</t>
+  </si>
+  <si>
+    <t>1 PKG / 5 KG</t>
+  </si>
+  <si>
+    <t>HC2608-2443</t>
+  </si>
+  <si>
+    <t>YJE123964101</t>
+  </si>
+  <si>
+    <t>160-13993851</t>
+  </si>
+  <si>
+    <t>1 PKG / 1.5 KG</t>
+  </si>
+  <si>
+    <t>HC2608-2444</t>
+  </si>
+  <si>
+    <t>2026004807</t>
+  </si>
+  <si>
+    <t>695-56377344</t>
+  </si>
+  <si>
+    <t>2 PKG / 23 KG</t>
+  </si>
+  <si>
+    <t>HC2608-2445</t>
+  </si>
+  <si>
+    <t>2026006574</t>
+  </si>
+  <si>
+    <t>2 PKG / 6.5 KG</t>
   </si>
   <si>
     <t>Shipper
@@ -207,7 +221,27 @@
     <t>CHIN HSIN TEXTILE</t>
   </si>
   <si>
-    <t>PRIME ASIA LEATHER CORPORATION TAIWAN</t>
+    <t>24.AUG.2026</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VAT</t>
+  </si>
+  <si>
+    <t>PPN 12%</t>
+  </si>
+  <si>
+    <t>PPN 12%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DAE SUNG HONG KONG LTD</t>
+  </si>
+  <si>
+    <t>DONGGUAN JUNSHENG FOOTWEAR PARTS COLTD</t>
+  </si>
+  <si>
+    <t>JADE LONG JOHN ENTERPRISE COLTD</t>
   </si>
   <si>
     <t>TIONG LIONG INDUSTRIAL COLTD</t>
@@ -248,7 +282,7 @@
       <charset val="136"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -258,6 +292,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF002060"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -276,7 +328,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -293,6 +345,39 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -629,7 +714,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCF1381F-552A-4924-9A7A-4C0080F73CE6}">
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:R22"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="17.36328125" customWidth="1"/>
@@ -637,20 +722,20 @@
     <col min="3" max="3" width="29.453125" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
     <col min="5" max="5" width="25.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.90625" customWidth="1"/>
-    <col min="7" max="7" width="29.26953125" customWidth="1"/>
-    <col min="8" max="9" width="13.7265625" customWidth="1"/>
-    <col min="10" max="10" width="17.6328125" customWidth="1"/>
-    <col min="11" max="11" width="20" customWidth="1"/>
-    <col min="12" max="12" width="16.90625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.6328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.36328125" customWidth="1"/>
-    <col min="15" max="15" width="7.6328125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.1796875" customWidth="1"/>
+    <col min="6" max="7" width="17.90625" customWidth="1"/>
+    <col min="8" max="8" width="29.26953125" customWidth="1"/>
+    <col min="9" max="10" width="13.7265625" customWidth="1"/>
+    <col min="11" max="11" width="17.6328125" customWidth="1"/>
+    <col min="12" max="12" width="20" customWidth="1"/>
+    <col min="13" max="13" width="16.90625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.6328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.36328125" customWidth="1"/>
+    <col min="16" max="16" width="7.6328125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.08984375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -670,757 +755,1155 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A2" s="4">
-        <v>46258</v>
+      <c r="R1" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A2" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F2">
         <v>159840</v>
       </c>
-      <c r="G2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H2" s="3">
-        <v>46250</v>
+      <c r="H2" t="s">
+        <v>30</v>
       </c>
       <c r="I2" s="3">
         <v>46250</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="3">
+        <v>46250</v>
+      </c>
+      <c r="K2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" t="s">
         <v>19</v>
       </c>
-      <c r="K2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="N2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2" t="s">
         <v>20</v>
       </c>
-      <c r="M2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N2" t="s">
-        <v>36</v>
-      </c>
-      <c r="O2" t="s">
-        <v>21</v>
-      </c>
-      <c r="P2" t="s">
-        <v>35</v>
-      </c>
       <c r="Q2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A3" s="4">
-        <v>46258</v>
+        <v>30</v>
+      </c>
+      <c r="R2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A3" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="B3" t="s">
         <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
-      <c r="G3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H3" s="3">
-        <v>46250</v>
+      <c r="H3" t="s">
+        <v>30</v>
       </c>
       <c r="I3" s="3">
         <v>46250</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="3">
+        <v>46250</v>
+      </c>
+      <c r="K3" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" t="s">
         <v>19</v>
       </c>
-      <c r="K3" t="s">
-        <v>34</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="N3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O3" t="s">
+        <v>31</v>
+      </c>
+      <c r="P3" t="s">
         <v>20</v>
       </c>
-      <c r="M3" t="s">
-        <v>35</v>
-      </c>
-      <c r="N3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P3" t="s">
-        <v>35</v>
-      </c>
       <c r="Q3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A4" s="4">
-        <v>46258</v>
+        <v>30</v>
+      </c>
+      <c r="R3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A4" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="B4" t="s">
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
-      <c r="G4" t="s">
-        <v>35</v>
-      </c>
-      <c r="H4" s="3">
-        <v>46250</v>
+      <c r="H4" t="s">
+        <v>30</v>
       </c>
       <c r="I4" s="3">
         <v>46250</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="3">
+        <v>46250</v>
+      </c>
+      <c r="K4" t="s">
+        <v>18</v>
+      </c>
+      <c r="L4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M4" t="s">
         <v>19</v>
       </c>
-      <c r="K4" t="s">
-        <v>34</v>
-      </c>
-      <c r="L4" t="s">
+      <c r="N4" t="s">
+        <v>30</v>
+      </c>
+      <c r="O4" t="s">
+        <v>31</v>
+      </c>
+      <c r="P4" t="s">
         <v>20</v>
       </c>
-      <c r="M4" t="s">
-        <v>35</v>
-      </c>
-      <c r="N4" t="s">
-        <v>36</v>
-      </c>
-      <c r="O4" t="s">
-        <v>21</v>
-      </c>
-      <c r="P4" t="s">
-        <v>35</v>
-      </c>
       <c r="Q4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A5" s="4">
-        <v>46258</v>
+        <v>30</v>
+      </c>
+      <c r="R4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="16" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="B5" t="s">
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F5" s="5">
         <v>4585728</v>
       </c>
-      <c r="G5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H5" s="3">
-        <v>46250</v>
+      <c r="H5" t="s">
+        <v>30</v>
       </c>
       <c r="I5" s="3">
         <v>46250</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="3">
+        <v>46250</v>
+      </c>
+      <c r="K5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5" t="s">
         <v>19</v>
       </c>
-      <c r="K5" t="s">
-        <v>34</v>
-      </c>
-      <c r="L5" t="s">
+      <c r="N5" t="s">
+        <v>30</v>
+      </c>
+      <c r="O5" t="s">
+        <v>31</v>
+      </c>
+      <c r="P5" t="s">
         <v>20</v>
       </c>
-      <c r="M5" t="s">
-        <v>35</v>
-      </c>
-      <c r="N5" t="s">
-        <v>36</v>
-      </c>
-      <c r="O5" t="s">
-        <v>21</v>
-      </c>
-      <c r="P5" t="s">
-        <v>35</v>
-      </c>
       <c r="Q5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A6" s="4">
-        <v>46258</v>
+        <v>30</v>
+      </c>
+      <c r="R5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A6" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="B6" t="s">
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" s="5">
-        <v>4203584</v>
-      </c>
-      <c r="G6" t="s">
-        <v>35</v>
-      </c>
-      <c r="H6" s="3">
-        <v>46250</v>
+        <v>51</v>
+      </c>
+      <c r="G6" s="5">
+        <v>504430</v>
+      </c>
+      <c r="H6" t="s">
+        <v>30</v>
       </c>
       <c r="I6" s="3">
         <v>46250</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="3">
+        <v>46250</v>
+      </c>
+      <c r="K6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M6" t="s">
         <v>19</v>
       </c>
-      <c r="K6" t="s">
+      <c r="N6" t="s">
+        <v>30</v>
+      </c>
+      <c r="O6" t="s">
+        <v>31</v>
+      </c>
+      <c r="P6" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" s="11" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="11">
+        <v>0</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" s="12">
+        <v>46246</v>
+      </c>
+      <c r="J7" s="12">
+        <v>46246</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="L7" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="L6" t="s">
-        <v>20</v>
-      </c>
-      <c r="M6" t="s">
+      <c r="M7" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="N7" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="O7" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="N6" t="s">
+      <c r="P7" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q7" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="R7" s="11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" s="11" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="11">
+        <v>0</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" s="12">
+        <v>46246</v>
+      </c>
+      <c r="J8" s="12">
+        <v>46246</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="N8" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="O8" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="P8" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q8" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="R8" s="11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" s="11" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="13">
+        <v>687720</v>
+      </c>
+      <c r="G9" s="13"/>
+      <c r="H9" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" s="12">
+        <v>46246</v>
+      </c>
+      <c r="J9" s="12">
+        <v>46246</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="N9" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="O9" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="P9" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q9" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="R9" s="11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" s="11" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="G10" s="13">
+        <v>75649</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="12">
+        <v>46246</v>
+      </c>
+      <c r="J10" s="12">
+        <v>46246</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="N10" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="O10" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="P10" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q10" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="R10" s="11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" s="7" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="O6" t="s">
+      <c r="C11" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="7">
+        <v>0</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I11" s="8">
+        <v>46247</v>
+      </c>
+      <c r="J11" s="8">
+        <v>46247</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="N11" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="O11" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P11" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P6" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q6" t="s">
+      <c r="Q11" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R11" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" s="7" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="7">
+        <v>0</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I12" s="8">
+        <v>46247</v>
+      </c>
+      <c r="J12" s="8">
+        <v>46247</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="N12" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="O12" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P12" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q12" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R12" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" s="7" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" s="9">
+        <v>214956</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I13" s="8">
+        <v>46247</v>
+      </c>
+      <c r="J13" s="8">
+        <v>46247</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="M13" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="O13" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P13" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q13" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R13" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" s="7" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" s="9">
+        <v>23645</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I14" s="8">
+        <v>46247</v>
+      </c>
+      <c r="J14" s="8">
+        <v>46247</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="N14" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="O14" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P14" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q14" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R14" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" s="15" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" s="15">
+        <v>0</v>
+      </c>
+      <c r="H15" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="I15" s="16">
+        <v>46246</v>
+      </c>
+      <c r="J15" s="16">
+        <v>46246</v>
+      </c>
+      <c r="K15" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="L15" s="15" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A7" s="4">
-        <v>46258</v>
-      </c>
-      <c r="B7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="M15" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="N15" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="O15" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="P15" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q15" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="R15" s="15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" s="15" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="15">
+        <v>0</v>
+      </c>
+      <c r="H16" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="I16" s="16">
+        <v>46246</v>
+      </c>
+      <c r="J16" s="16">
+        <v>46246</v>
+      </c>
+      <c r="K16" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="L16" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="M16" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="N16" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="O16" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="P16" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q16" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="R16" s="15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" s="15" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="F7">
+      <c r="F17" s="15">
+        <v>3110592</v>
+      </c>
+      <c r="H17" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="I17" s="16">
+        <v>46246</v>
+      </c>
+      <c r="J17" s="16">
+        <v>46246</v>
+      </c>
+      <c r="K17" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="L17" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="M17" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="N17" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="O17" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="P17" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q17" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="R17" s="15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" s="15" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="G18" s="15">
+        <v>342165</v>
+      </c>
+      <c r="H18" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="I18" s="16">
+        <v>46246</v>
+      </c>
+      <c r="J18" s="16">
+        <v>46246</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="L18" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="M18" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="N18" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="O18" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="P18" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q18" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="R18" s="15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A19" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19">
         <v>0</v>
       </c>
-      <c r="G7" t="s">
-        <v>35</v>
-      </c>
-      <c r="H7" s="3">
-        <v>46256</v>
-      </c>
-      <c r="I7" s="3">
-        <v>46256</v>
-      </c>
-      <c r="J7" t="s">
+      <c r="H19" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19" s="3">
+        <v>46246</v>
+      </c>
+      <c r="J19" s="3">
+        <v>46246</v>
+      </c>
+      <c r="K19" t="s">
+        <v>45</v>
+      </c>
+      <c r="L19" t="s">
+        <v>42</v>
+      </c>
+      <c r="M19" t="s">
         <v>22</v>
       </c>
-      <c r="K7" t="s">
-        <v>39</v>
-      </c>
-      <c r="L7" t="s">
-        <v>20</v>
-      </c>
-      <c r="M7" t="s">
-        <v>35</v>
-      </c>
-      <c r="N7" t="s">
+      <c r="N19" t="s">
+        <v>30</v>
+      </c>
+      <c r="O19" t="s">
+        <v>46</v>
+      </c>
+      <c r="P19" t="s">
         <v>23</v>
       </c>
-      <c r="O7" t="s">
-        <v>24</v>
-      </c>
-      <c r="P7" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A8" s="4">
-        <v>46258</v>
-      </c>
-      <c r="B8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8">
+      <c r="Q19" t="s">
+        <v>30</v>
+      </c>
+      <c r="R19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A20" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F20">
         <v>0</v>
       </c>
-      <c r="G8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H8" s="3">
-        <v>46256</v>
-      </c>
-      <c r="I8" s="3">
-        <v>46256</v>
-      </c>
-      <c r="J8" t="s">
+      <c r="H20" t="s">
+        <v>30</v>
+      </c>
+      <c r="I20" s="3">
+        <v>46246</v>
+      </c>
+      <c r="J20" s="3">
+        <v>46246</v>
+      </c>
+      <c r="K20" t="s">
+        <v>45</v>
+      </c>
+      <c r="L20" t="s">
+        <v>42</v>
+      </c>
+      <c r="M20" t="s">
         <v>22</v>
       </c>
-      <c r="K8" t="s">
-        <v>39</v>
-      </c>
-      <c r="L8" t="s">
-        <v>20</v>
-      </c>
-      <c r="M8" t="s">
-        <v>35</v>
-      </c>
-      <c r="N8" t="s">
+      <c r="N20" t="s">
+        <v>30</v>
+      </c>
+      <c r="O20" t="s">
+        <v>46</v>
+      </c>
+      <c r="P20" t="s">
         <v>23</v>
       </c>
-      <c r="O8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P8" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A9" s="4">
-        <v>46258</v>
-      </c>
-      <c r="B9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9" s="5">
-        <v>501564</v>
-      </c>
-      <c r="G9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H9" s="3">
-        <v>46256</v>
-      </c>
-      <c r="I9" s="3">
-        <v>46256</v>
-      </c>
-      <c r="J9" t="s">
+      <c r="Q20" t="s">
+        <v>30</v>
+      </c>
+      <c r="R20" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A21" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" t="s">
+        <v>28</v>
+      </c>
+      <c r="F21">
+        <v>879080</v>
+      </c>
+      <c r="H21" t="s">
+        <v>30</v>
+      </c>
+      <c r="I21" s="3">
+        <v>46246</v>
+      </c>
+      <c r="J21" s="3">
+        <v>46246</v>
+      </c>
+      <c r="K21" t="s">
+        <v>45</v>
+      </c>
+      <c r="L21" t="s">
+        <v>42</v>
+      </c>
+      <c r="M21" t="s">
         <v>22</v>
       </c>
-      <c r="K9" t="s">
-        <v>39</v>
-      </c>
-      <c r="L9" t="s">
-        <v>20</v>
-      </c>
-      <c r="M9" t="s">
-        <v>35</v>
-      </c>
-      <c r="N9" t="s">
+      <c r="N21" t="s">
+        <v>30</v>
+      </c>
+      <c r="O21" t="s">
+        <v>46</v>
+      </c>
+      <c r="P21" t="s">
         <v>23</v>
       </c>
-      <c r="O9" t="s">
-        <v>24</v>
-      </c>
-      <c r="P9" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A10" s="4">
-        <v>46258</v>
-      </c>
-      <c r="B10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10" s="5">
-        <v>459767</v>
-      </c>
-      <c r="G10" t="s">
-        <v>35</v>
-      </c>
-      <c r="H10" s="3">
-        <v>46256</v>
-      </c>
-      <c r="I10" s="3">
-        <v>46256</v>
-      </c>
-      <c r="J10" t="s">
+      <c r="Q21" t="s">
+        <v>30</v>
+      </c>
+      <c r="R21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A22" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" t="s">
+        <v>51</v>
+      </c>
+      <c r="G22">
+        <v>96699</v>
+      </c>
+      <c r="H22" t="s">
+        <v>30</v>
+      </c>
+      <c r="I22" s="3">
+        <v>46246</v>
+      </c>
+      <c r="J22" s="3">
+        <v>46246</v>
+      </c>
+      <c r="K22" t="s">
+        <v>45</v>
+      </c>
+      <c r="L22" t="s">
+        <v>42</v>
+      </c>
+      <c r="M22" t="s">
         <v>22</v>
       </c>
-      <c r="K10" t="s">
-        <v>39</v>
-      </c>
-      <c r="L10" t="s">
-        <v>20</v>
-      </c>
-      <c r="M10" t="s">
-        <v>35</v>
-      </c>
-      <c r="N10" t="s">
+      <c r="N22" t="s">
+        <v>30</v>
+      </c>
+      <c r="O22" t="s">
+        <v>46</v>
+      </c>
+      <c r="P22" t="s">
         <v>23</v>
       </c>
-      <c r="O10" t="s">
-        <v>24</v>
-      </c>
-      <c r="P10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A11" s="4">
-        <v>46258</v>
-      </c>
-      <c r="B11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" t="s">
-        <v>28</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11" t="s">
-        <v>35</v>
-      </c>
-      <c r="H11" s="3">
-        <v>46253</v>
-      </c>
-      <c r="I11" s="3">
-        <v>46253</v>
-      </c>
-      <c r="J11">
-        <v>2026006792</v>
-      </c>
-      <c r="K11" t="s">
-        <v>40</v>
-      </c>
-      <c r="L11" t="s">
-        <v>25</v>
-      </c>
-      <c r="M11" t="s">
-        <v>35</v>
-      </c>
-      <c r="N11" t="s">
-        <v>26</v>
-      </c>
-      <c r="O11" t="s">
-        <v>27</v>
-      </c>
-      <c r="P11" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A12" s="4">
-        <v>46258</v>
-      </c>
-      <c r="B12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12" t="s">
-        <v>35</v>
-      </c>
-      <c r="H12" s="3">
-        <v>46253</v>
-      </c>
-      <c r="I12" s="3">
-        <v>46253</v>
-      </c>
-      <c r="J12">
-        <v>2026006792</v>
-      </c>
-      <c r="K12" t="s">
-        <v>40</v>
-      </c>
-      <c r="L12" t="s">
-        <v>25</v>
-      </c>
-      <c r="M12" t="s">
-        <v>35</v>
-      </c>
-      <c r="N12" t="s">
-        <v>26</v>
-      </c>
-      <c r="O12" t="s">
-        <v>27</v>
-      </c>
-      <c r="P12" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A13" s="4">
-        <v>46258</v>
-      </c>
-      <c r="B13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" t="s">
-        <v>38</v>
-      </c>
-      <c r="F13" s="5">
-        <v>4690609</v>
-      </c>
-      <c r="G13" t="s">
-        <v>35</v>
-      </c>
-      <c r="H13" s="3">
-        <v>46253</v>
-      </c>
-      <c r="I13" s="3">
-        <v>46253</v>
-      </c>
-      <c r="J13">
-        <v>2026006792</v>
-      </c>
-      <c r="K13" t="s">
-        <v>40</v>
-      </c>
-      <c r="L13" t="s">
-        <v>25</v>
-      </c>
-      <c r="M13" t="s">
-        <v>35</v>
-      </c>
-      <c r="N13" t="s">
-        <v>26</v>
-      </c>
-      <c r="O13" t="s">
-        <v>27</v>
-      </c>
-      <c r="P13" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A14" s="4">
-        <v>46258</v>
-      </c>
-      <c r="B14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" t="s">
-        <v>33</v>
-      </c>
-      <c r="F14" s="5">
-        <v>4299725</v>
-      </c>
-      <c r="G14" t="s">
-        <v>35</v>
-      </c>
-      <c r="H14" s="3">
-        <v>46253</v>
-      </c>
-      <c r="I14" s="3">
-        <v>46253</v>
-      </c>
-      <c r="J14">
-        <v>2026006792</v>
-      </c>
-      <c r="K14" t="s">
-        <v>40</v>
-      </c>
-      <c r="L14" t="s">
-        <v>25</v>
-      </c>
-      <c r="M14" t="s">
-        <v>35</v>
-      </c>
-      <c r="N14" t="s">
-        <v>26</v>
-      </c>
-      <c r="O14" t="s">
-        <v>27</v>
-      </c>
-      <c r="P14" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A15" s="4"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A16" s="4"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A17" s="4"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A18" s="4"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A19" s="4"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A20" s="4"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
+      <c r="Q22" t="s">
+        <v>30</v>
+      </c>
+      <c r="R22" t="s">
+        <v>56</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
